--- a/tests/e2e/scenarios/ctsp_industry/agents.xlsx
+++ b/tests/e2e/scenarios/ctsp_industry/agents.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="182">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -350,22 +350,22 @@
     <t>ev/charging_scheme/method</t>
   </si>
   <si>
-    <t>ev/charging_scheme/price_sensitive_threshold</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc_val</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc_time_val</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc_time_time</t>
+    <t>ev/charging_scheme/price_sensitive/threshold</t>
+  </si>
+  <si>
+    <t>ev/charging_scheme/min_soc/val</t>
+  </si>
+  <si>
+    <t>ev/charging_scheme/min_soc_time/val</t>
+  </si>
+  <si>
+    <t>ev/charging_scheme/min_soc_time/time</t>
   </si>
   <si>
     <t>ev/fcast/method</t>
   </si>
   <si>
-    <t>ev/fcast/random_forest_classifier/features</t>
+    <t>ev/fcast/rfr/features</t>
   </si>
   <si>
     <t>battery/owner</t>
@@ -491,7 +491,13 @@
     <t>pv_1_pu.csv</t>
   </si>
   <si>
-    <t>ev_close</t>
+    <t>ev_fulltime_42.csv</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>arrival</t>
   </si>
   <si>
     <t>time</t>
@@ -542,22 +548,7 @@
     <t>ev/sizing/v2h_1</t>
   </si>
   <si>
-    <t>ev/charging_scheme/price_sensitive/threshold</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc/val</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc_time/val</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc_time/time</t>
-  </si>
-  <si>
-    <t>ev/fcast/rfr/features</t>
-  </si>
-  <si>
-    <t>8KC3tljdla5ArmK</t>
+    <t>C3tljdla5ArmKf1</t>
   </si>
   <si>
     <t>food</t>
@@ -566,7 +557,10 @@
     <t>food_pu_0.csv</t>
   </si>
   <si>
-    <t>arrival</t>
+    <t>pv_2_pu.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_2.csv</t>
   </si>
 </sst>
 </file>
@@ -1654,16 +1648,58 @@
         <v>3</v>
       </c>
       <c r="CW2">
+        <v>1</v>
+      </c>
+      <c r="CX2">
+        <v>1</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ2">
+        <v>50000</v>
+      </c>
+      <c r="DA2">
+        <v>7200</v>
+      </c>
+      <c r="DB2">
+        <v>11000</v>
+      </c>
+      <c r="DC2">
+        <v>100000</v>
+      </c>
+      <c r="DD2">
+        <v>0.9</v>
+      </c>
+      <c r="DE2">
+        <v>0.8</v>
+      </c>
+      <c r="DF2" t="b">
         <v>0</v>
       </c>
-      <c r="CX2">
+      <c r="DG2" t="b">
         <v>0</v>
       </c>
+      <c r="DH2" t="s">
+        <v>159</v>
+      </c>
+      <c r="DI2">
+        <v>0.05</v>
+      </c>
+      <c r="DJ2">
+        <v>0.5</v>
+      </c>
+      <c r="DK2">
+        <v>0.8</v>
+      </c>
+      <c r="DL2">
+        <v>8.5</v>
+      </c>
       <c r="DM2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="DN2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="DO2">
         <v>1</v>
@@ -1687,34 +1723,34 @@
         <v>0</v>
       </c>
       <c r="DW2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="DX2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="DY2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="DZ2">
         <v>120</v>
       </c>
       <c r="EA2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="EB2">
         <v>86400</v>
       </c>
       <c r="EC2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="ED2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="EE2">
         <v>120</v>
       </c>
       <c r="EF2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="EG2">
         <v>72000</v>
@@ -1726,31 +1762,31 @@
         <v>0</v>
       </c>
       <c r="EJ2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="EK2">
         <v>1</v>
       </c>
       <c r="EL2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="EM2">
         <v>1</v>
       </c>
       <c r="EN2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="EO2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="EP2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="EQ2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="ER2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="ES2">
         <v>86400</v>
@@ -2104,52 +2140,52 @@
         <v>109</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="DQ1" s="1" t="s">
         <v>110</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="DV1" s="1" t="s">
         <v>115</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="DX1" s="1" t="s">
         <v>117</v>
@@ -2256,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G2">
         <v>4501</v>
@@ -2274,7 +2310,7 @@
         <v>1063000000</v>
       </c>
       <c r="K2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L2" t="s">
         <v>153</v>
@@ -2340,7 +2376,7 @@
         <v>1401000000</v>
       </c>
       <c r="AG2" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -2526,16 +2562,58 @@
         <v>3</v>
       </c>
       <c r="CW2">
+        <v>1</v>
+      </c>
+      <c r="CX2">
+        <v>1</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>181</v>
+      </c>
+      <c r="CZ2">
+        <v>500000</v>
+      </c>
+      <c r="DA2">
+        <v>7200</v>
+      </c>
+      <c r="DB2">
+        <v>11000</v>
+      </c>
+      <c r="DC2">
+        <v>100000</v>
+      </c>
+      <c r="DD2">
+        <v>0.9</v>
+      </c>
+      <c r="DE2">
+        <v>0.8</v>
+      </c>
+      <c r="DF2" t="b">
         <v>0</v>
       </c>
-      <c r="CX2">
+      <c r="DG2" t="b">
         <v>0</v>
       </c>
+      <c r="DQ2" t="s">
+        <v>159</v>
+      </c>
+      <c r="DR2">
+        <v>0.05</v>
+      </c>
+      <c r="DS2">
+        <v>0.5</v>
+      </c>
+      <c r="DT2">
+        <v>0.8</v>
+      </c>
+      <c r="DU2">
+        <v>8.5</v>
+      </c>
       <c r="DV2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="DW2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="DX2">
         <v>1</v>
@@ -2559,34 +2637,34 @@
         <v>0</v>
       </c>
       <c r="EF2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="EG2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="EH2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="EI2">
         <v>120</v>
       </c>
       <c r="EJ2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="EK2">
         <v>86400</v>
       </c>
       <c r="EL2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="EM2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="EN2">
         <v>120</v>
       </c>
       <c r="EO2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="EP2">
         <v>57600</v>
@@ -2598,31 +2676,31 @@
         <v>0</v>
       </c>
       <c r="ES2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="ET2">
         <v>1</v>
       </c>
       <c r="EU2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="EV2">
         <v>1</v>
       </c>
       <c r="EW2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="EX2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="EY2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="EZ2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="FA2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="FB2">
         <v>86400</v>
